--- a/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_SFH_until_2004_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_SFH_until_2004_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>210.0891942897042</v>
+        <v>123.6710750153762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>38837.35169307082</v>
       </c>
       <c r="F2" t="n">
-        <v>181.6897148629526</v>
+        <v>139.007650765141</v>
       </c>
       <c r="G2" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="H2" t="n">
-        <v>159.74597322713</v>
+        <v>123.6710750153762</v>
       </c>
       <c r="I2" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="J2" t="n">
-        <v>189.1949461796613</v>
+        <v>129.0111315749261</v>
       </c>
       <c r="K2" t="n">
         <v>38837.35169307082</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>283.4638942069081</v>
+        <v>123.6710750153762</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>38837.35169307082</v>
       </c>
       <c r="F3" t="n">
-        <v>279.9444063054141</v>
+        <v>139.007650765141</v>
       </c>
       <c r="G3" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="H3" t="n">
-        <v>213.08837136766</v>
+        <v>123.6710750153762</v>
       </c>
       <c r="I3" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="J3" t="n">
-        <v>256.1400910136603</v>
+        <v>129.0111315749261</v>
       </c>
       <c r="K3" t="n">
         <v>38837.35169307082</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>283.4638942069081</v>
+        <v>123.6710750153762</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>38837.35169307082</v>
       </c>
       <c r="F4" t="n">
-        <v>279.9444063054141</v>
+        <v>139.007650765141</v>
       </c>
       <c r="G4" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="H4" t="n">
-        <v>213.08837136766</v>
+        <v>123.6710750153762</v>
       </c>
       <c r="I4" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="J4" t="n">
-        <v>256.1400910136603</v>
+        <v>129.0111315749261</v>
       </c>
       <c r="K4" t="n">
         <v>38837.35169307082</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>338.697142804643</v>
+        <v>157.5154765243714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>38837.35169307082</v>
       </c>
       <c r="F5" t="n">
-        <v>346.0434120712278</v>
+        <v>158.889401304883</v>
       </c>
       <c r="G5" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="H5" t="n">
-        <v>213.08837136766</v>
+        <v>123.6710750153762</v>
       </c>
       <c r="I5" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="J5" t="n">
-        <v>256.1400910136603</v>
+        <v>129.0111315749261</v>
       </c>
       <c r="K5" t="n">
         <v>38837.35169307082</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>338.697142804643</v>
+        <v>198.9577826575259</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>38837.35169307082</v>
       </c>
       <c r="F6" t="n">
-        <v>346.0434120712278</v>
+        <v>201.8797072984663</v>
       </c>
       <c r="G6" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="H6" t="n">
-        <v>213.08837136766</v>
+        <v>183.5503580721385</v>
       </c>
       <c r="I6" t="n">
         <v>38837.35169307082</v>
       </c>
       <c r="J6" t="n">
-        <v>256.1400910136603</v>
+        <v>187.9335328196375</v>
       </c>
       <c r="K6" t="n">
         <v>38837.35169307082</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>31.0782777297697</v>
+        <v>27.06194068034541</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>31.0782777297697</v>
+        <v>27.06194068034541</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>40.86895297045228</v>
+        <v>35.58733822288941</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>40.86895297045228</v>
+        <v>35.58733822288941</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>45.40937505920294</v>
+        <v>39.54098823843713</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>45.40937505920294</v>
+        <v>39.54098823843713</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>47.97116084716269</v>
+        <v>41.77170692987578</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>47.97116084716269</v>
+        <v>41.77170692987578</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>58.25602753960624</v>
+        <v>50.72743011235955</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>49.60362123854942</v>
+        <v>43.19319967342005</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>49.60362123854942</v>
+        <v>43.19319967342005</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.007853373487058824</v>
+        <v>0.007511922465882353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007853373487058824</v>
+        <v>0.007511922465882353</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.007853373487058824</v>
+        <v>0.007511922465882353</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.007853373487058824</v>
+        <v>0.007511922465882353</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.008536275529411764</v>
+        <v>0.007853373487058824</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.008536275529411764</v>
+        <v>0.007983885327894022</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.008536275529411764</v>
+        <v>0.007853373487058824</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.008536275529411764</v>
+        <v>0.007853373487058824</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008054909494705133</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008194824508235296</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008077099385217324</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008115589009916482</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008054909494705133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008194824508235294</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008077099385217324</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008115589009916482</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008473979795725364</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008405763688576569</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008194824508235294</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.009219177571764709</v>
+        <v>0.008194824508235294</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.2997901194298725</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>6.094900728</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.112061439556301</v>
       </c>
       <c r="G18" t="n">
         <v>6.094900728</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.312764804220579</v>
       </c>
       <c r="I18" t="n">
         <v>6.094900728</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.2266323224681212</v>
       </c>
       <c r="K18" t="n">
         <v>6.094900728</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.6185174159378987</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>6.094900728</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.5441875649999997</v>
       </c>
       <c r="G19" t="n">
         <v>6.094900728</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.6067290366032979</v>
       </c>
       <c r="I19" t="n">
         <v>6.094900728</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.5862814234818695</v>
       </c>
       <c r="K19" t="n">
         <v>6.094900728</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.6185174159378988</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>6.094900728</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.5441875650000005</v>
       </c>
       <c r="G20" t="n">
         <v>6.094900728</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.6067290366032979</v>
       </c>
       <c r="I20" t="n">
         <v>6.094900728</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.5862814234818695</v>
       </c>
       <c r="K20" t="n">
         <v>6.094900728</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.3958863185209012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>6.094900728</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.4321261254436987</v>
       </c>
       <c r="G21" t="n">
         <v>6.094900728</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.5441875650000005</v>
       </c>
       <c r="I21" t="n">
         <v>6.094900728</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.5441875650000005</v>
       </c>
       <c r="K21" t="n">
         <v>6.094900728</v>
@@ -2344,7 +2344,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>4.270179437209341</v>
+        <v>3.426188129225436</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2358,19 +2358,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F52" t="n">
-        <v>2.735791535777964</v>
+        <v>1.953603916752497</v>
       </c>
       <c r="G52" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H52" t="n">
-        <v>8.65371341664004</v>
+        <v>3.042227440633076</v>
       </c>
       <c r="I52" t="n">
         <v>13.52031262959309</v>
       </c>
       <c r="J52" t="n">
-        <v>10.25806588508666</v>
+        <v>1.437149477975393</v>
       </c>
       <c r="K52" t="n">
         <v>13.52031262959309</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>8.039633880591257</v>
+        <v>8.734768846129679</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F53" t="n">
-        <v>6.711025613548538</v>
+        <v>7.665615876729595</v>
       </c>
       <c r="G53" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H53" t="n">
-        <v>12.13150922174119</v>
+        <v>8.350808157537321</v>
       </c>
       <c r="I53" t="n">
         <v>19.55287676772119</v>
       </c>
       <c r="J53" t="n">
-        <v>14.26013401626071</v>
+        <v>6.574116931491154</v>
       </c>
       <c r="K53" t="n">
         <v>19.55287676772119</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>11.21881241428852</v>
+        <v>12.99509892452415</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F54" t="n">
-        <v>10.22684895495872</v>
+        <v>11.76699273094411</v>
       </c>
       <c r="G54" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H54" t="n">
-        <v>16.48276765702635</v>
+        <v>12.61113823593179</v>
       </c>
       <c r="I54" t="n">
         <v>22.83286523994727</v>
       </c>
       <c r="J54" t="n">
-        <v>17.58356673110471</v>
+        <v>10.92455446290426</v>
       </c>
       <c r="K54" t="n">
         <v>22.83286523994727</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>18.66935597301676</v>
+        <v>18.6369073326049</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F55" t="n">
-        <v>17.87058883919096</v>
+        <v>17.77538926237083</v>
       </c>
       <c r="G55" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H55" t="n">
-        <v>16.55221227921145</v>
+        <v>18.57785036545613</v>
       </c>
       <c r="I55" t="n">
         <v>24.85194871132677</v>
       </c>
       <c r="J55" t="n">
-        <v>18.50790859186868</v>
+        <v>16.95756946960079</v>
       </c>
       <c r="K55" t="n">
         <v>24.85194871132677</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>18.66935597301676</v>
+        <v>18.29976824065395</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F56" t="n">
-        <v>17.03264291079557</v>
+        <v>17.38533114072048</v>
       </c>
       <c r="G56" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H56" t="n">
-        <v>15.52379261972352</v>
+        <v>18.34966735147765</v>
       </c>
       <c r="I56" t="n">
         <v>26.2078323626014</v>
       </c>
       <c r="J56" t="n">
-        <v>18.09248527011509</v>
+        <v>17.00733709408518</v>
       </c>
       <c r="K56" t="n">
         <v>26.2078323626014</v>
@@ -2714,7 +2714,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>2.270680794633573</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2728,19 +2728,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F62" t="n">
-        <v>3.694324515225559</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H62" t="n">
-        <v>5.617173534829096</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="J62" t="n">
-        <v>3.363211368900167</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>46.89428355486757</v>
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>3.025283771491148</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,19 +2765,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F63" t="n">
-        <v>3.694324515225559</v>
+        <v>0.01380913759068719</v>
       </c>
       <c r="G63" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H63" t="n">
-        <v>6.40940200253187</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="J63" t="n">
-        <v>4.027029078918669</v>
+        <v>0.3462303002026564</v>
       </c>
       <c r="K63" t="n">
         <v>46.89428355486757</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>7.846105237793891</v>
+        <v>3.737597650515399</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F64" t="n">
-        <v>8.178501173815377</v>
+        <v>3.910398495621159</v>
       </c>
       <c r="G64" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H64" t="n">
-        <v>10.05814356724672</v>
+        <v>3.737091298218958</v>
       </c>
       <c r="I64" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="J64" t="n">
-        <v>8.703596364074661</v>
+        <v>3.992991225516813</v>
       </c>
       <c r="K64" t="n">
         <v>46.89428355486757</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>7.202589513762008</v>
+        <v>3.737597650515399</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F65" t="n">
-        <v>7.839306590236666</v>
+        <v>4.584307358213905</v>
       </c>
       <c r="G65" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H65" t="n">
-        <v>11.3945927732268</v>
+        <v>4.117643897159459</v>
       </c>
       <c r="I65" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="J65" t="n">
-        <v>9.185148331475878</v>
+        <v>5.683891629323375</v>
       </c>
       <c r="K65" t="n">
         <v>46.89428355486757</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>8.025283771491154</v>
+        <v>3.737597650515399</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F66" t="n">
-        <v>9.499946776361199</v>
+        <v>4.570498220623217</v>
       </c>
       <c r="G66" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H66" t="n">
-        <v>13.94162884765902</v>
+        <v>4.117643897159459</v>
       </c>
       <c r="I66" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="J66" t="n">
-        <v>10.42326591095862</v>
+        <v>5.337661329120718</v>
       </c>
       <c r="K66" t="n">
         <v>46.89428355486757</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1.025153964783601</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1.025153964783601</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1.786633691546775</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1.786633691546775</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>2.416998279213877</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>2.416998279213877</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>2.95649040365484</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>2.95649040365484</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>3.426365170187669</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>3.426365170187669</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="77">
@@ -3269,7 +3269,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>8.025408318469921</v>
+        <v>5.963936381034648</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3283,22 +3283,22 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F77" t="n">
-        <v>8.762611604311189</v>
+        <v>6.869914601660793</v>
       </c>
       <c r="G77" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H77" t="n">
-        <v>1.405893828165188</v>
+        <v>6.347897069627007</v>
       </c>
       <c r="I77" t="n">
-        <v>1.025153964783601</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J77" t="n">
-        <v>1.405893828165188</v>
+        <v>7.724676900898182</v>
       </c>
       <c r="K77" t="n">
-        <v>1.025153964783601</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="78">
@@ -3306,7 +3306,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>8.025408318469921</v>
+        <v>5.963936381034648</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3320,22 +3320,22 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F78" t="n">
-        <v>8.762611604311189</v>
+        <v>6.869914601660793</v>
       </c>
       <c r="G78" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H78" t="n">
-        <v>2.101815985380326</v>
+        <v>6.347897069627007</v>
       </c>
       <c r="I78" t="n">
-        <v>1.786633691546775</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J78" t="n">
-        <v>1.405893828165188</v>
+        <v>7.724676900898182</v>
       </c>
       <c r="K78" t="n">
-        <v>1.786633691546775</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="79">
@@ -3343,7 +3343,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>8.025408318469921</v>
+        <v>5.963936381034648</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3357,22 +3357,22 @@
         <v>46.89428355486757</v>
       </c>
       <c r="F79" t="n">
-        <v>8.762611604311189</v>
+        <v>6.869914601660793</v>
       </c>
       <c r="G79" t="n">
         <v>46.89428355486757</v>
       </c>
       <c r="H79" t="n">
-        <v>2.101815985380326</v>
+        <v>6.347897069627008</v>
       </c>
       <c r="I79" t="n">
-        <v>2.416998279213877</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J79" t="n">
-        <v>1.405893828165188</v>
+        <v>7.724676900898182</v>
       </c>
       <c r="K79" t="n">
-        <v>2.416998279213877</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="80">
@@ -3400,16 +3400,16 @@
         <v>46.89428355486757</v>
       </c>
       <c r="H80" t="n">
-        <v>0.6959221572151382</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>2.95649040365484</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>2.95649040365484</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>3.426365170187669</v>
+        <v>46.89428355486757</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>3.426365170187669</v>
+        <v>46.89428355486757</v>
       </c>
     </row>
     <row r="82">
